--- a/pages/Skinsuit/Measurements.xlsx
+++ b/pages/Skinsuit/Measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Skinsuit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1E20DB-9CCC-4B7A-82EC-0F33656D1924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0898B043-23E7-4E4A-AC7A-577414DA92D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{AA45E310-34C1-48BF-B6B0-D77B00EDA5C9}"/>
   </bookViews>
@@ -293,10 +293,10 @@
     <t>https://i.ibb.co/mGmGPSv/Bryony-Trimmed.jpg</t>
   </si>
   <si>
-    <t>https://i.ibb.co/n3t1m7J/Ally-Trimmed.jpg</t>
-  </si>
-  <si>
     <t>https://i.ibb.co/tHkSCvY/Tom-Trimmed.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/6gHpCxT/Ally-Trimmed.jpg</t>
   </si>
 </sst>
 </file>
@@ -354,11 +354,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1340,10 +1339,10 @@
       <c r="C6">
         <v>0.32545617293022139</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>72.2</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>182.5</v>
       </c>
       <c r="F6">
@@ -1458,7 +1457,7 @@
         <v>10</v>
       </c>
       <c r="AQ6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.45">
@@ -1720,7 +1719,7 @@
         <v>11</v>
       </c>
       <c r="AQ8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.45">

--- a/pages/Skinsuit/Measurements.xlsx
+++ b/pages/Skinsuit/Measurements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Skinsuit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0898B043-23E7-4E4A-AC7A-577414DA92D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD06BFD3-983F-452E-819F-A67CE4C14491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{AA45E310-34C1-48BF-B6B0-D77B00EDA5C9}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA45E310-34C1-48BF-B6B0-D77B00EDA5C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
   <si>
     <t>George Jackson</t>
   </si>
@@ -298,12 +298,42 @@
   <si>
     <t>https://i.ibb.co/6gHpCxT/Ally-Trimmed.jpg</t>
   </si>
+  <si>
+    <t>Sam Dakin</t>
+  </si>
+  <si>
+    <t>Michaella Drummond</t>
+  </si>
+  <si>
+    <t>Sami Donnelly</t>
+  </si>
+  <si>
+    <t>Prue Fowler</t>
+  </si>
+  <si>
+    <t>Nicole Shields</t>
+  </si>
+  <si>
+    <t>Campbell Stewart</t>
+  </si>
+  <si>
+    <t>Aaron Gate</t>
+  </si>
+  <si>
+    <t>Corbin Strong</t>
+  </si>
+  <si>
+    <t>Nick Kergozou</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +354,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -333,7 +370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -350,14 +387,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804CFD34-F887-40CD-BE87-6B54EBE5BE66}">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.3984375" bestFit="1" customWidth="1"/>
@@ -871,438 +923,359 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="C2">
-        <v>0.32858719322387142</v>
-      </c>
-      <c r="D2">
-        <v>81.2</v>
-      </c>
-      <c r="E2">
-        <v>179.5</v>
-      </c>
-      <c r="F2">
-        <v>133</v>
-      </c>
-      <c r="G2">
+      <c r="D2" s="5">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="E2" s="5">
+        <v>181</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5">
+        <v>38</v>
+      </c>
+      <c r="H2" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="I2" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="J2" s="5">
+        <v>27</v>
+      </c>
+      <c r="K2" s="5">
+        <v>27</v>
+      </c>
+      <c r="L2" s="5">
+        <v>22</v>
+      </c>
+      <c r="M2" s="5">
+        <v>18</v>
+      </c>
+      <c r="N2" s="5">
+        <v>97.5</v>
+      </c>
+      <c r="O2" s="5">
+        <v>95</v>
+      </c>
+      <c r="P2" s="5">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>101</v>
+      </c>
+      <c r="R2" s="5">
+        <v>59</v>
+      </c>
+      <c r="S2" s="5">
+        <v>55.5</v>
+      </c>
+      <c r="T2" s="5">
+        <v>41</v>
+      </c>
+      <c r="U2" s="5">
         <v>39</v>
       </c>
-      <c r="H2">
-        <v>32.5</v>
-      </c>
-      <c r="I2">
-        <v>33.5</v>
-      </c>
-      <c r="J2">
-        <v>29.5</v>
-      </c>
-      <c r="K2">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>26.5</v>
-      </c>
-      <c r="M2">
-        <v>17</v>
-      </c>
-      <c r="N2">
-        <v>101.5</v>
-      </c>
-      <c r="O2">
-        <v>98.5</v>
-      </c>
-      <c r="P2">
-        <v>87.5</v>
-      </c>
-      <c r="Q2">
-        <v>96</v>
-      </c>
-      <c r="R2">
-        <v>58</v>
-      </c>
-      <c r="S2">
-        <v>56</v>
-      </c>
-      <c r="T2">
-        <v>39</v>
-      </c>
-      <c r="U2">
-        <v>37.5</v>
-      </c>
-      <c r="V2">
-        <v>37</v>
-      </c>
-      <c r="W2">
-        <v>33</v>
-      </c>
-      <c r="X2">
-        <v>23</v>
-      </c>
-      <c r="Y2">
-        <v>28</v>
-      </c>
-      <c r="Z2">
-        <v>32</v>
-      </c>
-      <c r="AA2">
-        <v>26.5</v>
-      </c>
-      <c r="AB2">
-        <v>91.5</v>
-      </c>
-      <c r="AC2">
-        <v>42.5</v>
-      </c>
-      <c r="AD2">
-        <v>48.5</v>
-      </c>
-      <c r="AE2">
-        <v>41.5</v>
-      </c>
-      <c r="AF2">
-        <v>51</v>
-      </c>
-      <c r="AG2">
-        <v>9.5</v>
-      </c>
-      <c r="AH2">
-        <v>11</v>
-      </c>
-      <c r="AI2">
-        <v>8</v>
-      </c>
-      <c r="AJ2">
-        <v>9</v>
-      </c>
-      <c r="AK2">
-        <v>9.5</v>
-      </c>
-      <c r="AL2">
-        <v>10</v>
-      </c>
-      <c r="AM2">
-        <v>18</v>
-      </c>
-      <c r="AN2">
-        <v>19</v>
-      </c>
-      <c r="AO2">
-        <v>11</v>
-      </c>
-      <c r="AP2">
-        <v>11</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>67</v>
-      </c>
+      <c r="V2" s="5">
+        <v>35</v>
+      </c>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5">
+        <v>49</v>
+      </c>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="C3">
-        <v>0.34210564989111703</v>
-      </c>
-      <c r="D3">
-        <v>76</v>
-      </c>
-      <c r="E3">
-        <v>188</v>
-      </c>
-      <c r="F3">
-        <v>136.5</v>
-      </c>
-      <c r="G3">
-        <v>38</v>
-      </c>
-      <c r="H3">
-        <v>29</v>
-      </c>
-      <c r="I3">
-        <v>30.5</v>
-      </c>
-      <c r="J3">
-        <v>26.5</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
-      </c>
-      <c r="N3">
-        <v>93</v>
-      </c>
-      <c r="O3">
-        <v>86.5</v>
-      </c>
-      <c r="P3">
-        <v>75.5</v>
-      </c>
-      <c r="Q3">
-        <v>93</v>
-      </c>
-      <c r="R3">
+      <c r="D3" s="5">
+        <v>76.5</v>
+      </c>
+      <c r="E3" s="5">
+        <v>179.5</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>37.5</v>
+      </c>
+      <c r="H3" s="5">
+        <v>31</v>
+      </c>
+      <c r="I3" s="5">
+        <v>32</v>
+      </c>
+      <c r="J3" s="5">
+        <v>28</v>
+      </c>
+      <c r="K3" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="L3" s="5">
+        <v>23.5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>18</v>
+      </c>
+      <c r="N3" s="5">
+        <v>99</v>
+      </c>
+      <c r="O3" s="5">
+        <v>94</v>
+      </c>
+      <c r="P3" s="5">
+        <v>83</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>99</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
         <v>56</v>
       </c>
-      <c r="S3">
-        <v>54.5</v>
-      </c>
-      <c r="T3">
-        <v>40</v>
-      </c>
-      <c r="U3">
-        <v>38</v>
-      </c>
-      <c r="V3">
-        <v>37.5</v>
-      </c>
-      <c r="W3">
-        <v>33</v>
-      </c>
-      <c r="X3">
-        <v>23.5</v>
-      </c>
-      <c r="Y3">
-        <v>27.5</v>
-      </c>
-      <c r="Z3">
-        <v>32.5</v>
-      </c>
-      <c r="AA3">
-        <v>27</v>
-      </c>
-      <c r="AB3">
-        <v>96</v>
-      </c>
-      <c r="AC3">
-        <v>43.5</v>
-      </c>
-      <c r="AD3">
-        <v>53</v>
-      </c>
-      <c r="AE3">
-        <v>44.5</v>
-      </c>
-      <c r="AF3">
-        <v>47</v>
-      </c>
-      <c r="AG3">
-        <v>9</v>
-      </c>
-      <c r="AH3">
-        <v>10.5</v>
-      </c>
-      <c r="AI3">
-        <v>7.5</v>
-      </c>
-      <c r="AJ3">
-        <v>8.5</v>
-      </c>
-      <c r="AK3">
-        <v>9.5</v>
-      </c>
-      <c r="AL3">
-        <v>9</v>
-      </c>
-      <c r="AM3">
-        <v>17.5</v>
-      </c>
-      <c r="AN3">
-        <v>18</v>
-      </c>
-      <c r="AO3">
-        <v>11</v>
-      </c>
-      <c r="AP3">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>64</v>
-      </c>
+      <c r="T3" s="5">
+        <v>44</v>
+      </c>
+      <c r="U3" s="5">
+        <v>37</v>
+      </c>
+      <c r="V3" s="5">
+        <v>36</v>
+      </c>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5">
+        <v>48</v>
+      </c>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
     </row>
     <row r="4" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="2">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="E4" s="2">
-        <v>178</v>
-      </c>
-      <c r="G4">
-        <v>38</v>
-      </c>
-      <c r="H4">
-        <v>27</v>
-      </c>
-      <c r="J4">
-        <v>26</v>
-      </c>
-      <c r="K4">
-        <v>26</v>
-      </c>
-      <c r="L4">
-        <v>23</v>
-      </c>
-      <c r="M4">
-        <v>17</v>
-      </c>
-      <c r="N4">
-        <v>94</v>
-      </c>
-      <c r="O4">
-        <v>89</v>
-      </c>
-      <c r="P4">
-        <v>76</v>
-      </c>
-      <c r="Q4">
-        <v>94</v>
-      </c>
-      <c r="R4">
-        <v>53.5</v>
-      </c>
-      <c r="S4">
+      <c r="D4" s="5">
+        <v>67.3</v>
+      </c>
+      <c r="E4" s="5">
+        <v>171.5</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28.5</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
+        <v>26.5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="N4" s="5">
+        <v>95</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>96</v>
+      </c>
+      <c r="R4" s="5">
+        <v>56.5</v>
+      </c>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5">
+        <v>35</v>
+      </c>
+      <c r="V4" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5">
         <v>48</v>
       </c>
-      <c r="T4">
-        <v>40</v>
-      </c>
-      <c r="V4">
-        <v>38</v>
-      </c>
-      <c r="W4">
-        <v>30</v>
-      </c>
-      <c r="X4">
-        <v>21.5</v>
-      </c>
-      <c r="Y4">
-        <v>25</v>
-      </c>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5">
-        <v>0.34157138849180374</v>
+        <v>0.32858719322387142</v>
       </c>
       <c r="D5">
-        <v>73.3</v>
+        <v>81.2</v>
       </c>
       <c r="E5">
-        <v>183</v>
+        <v>179.5</v>
       </c>
       <c r="F5">
         <v>133</v>
       </c>
       <c r="G5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="I5">
-        <v>31.5</v>
+        <v>33.5</v>
       </c>
       <c r="J5">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="K5">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="L5">
         <v>26.5</v>
       </c>
       <c r="M5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="N5">
-        <v>94</v>
+        <v>101.5</v>
       </c>
       <c r="O5">
-        <v>89</v>
+        <v>98.5</v>
       </c>
       <c r="P5">
-        <v>75.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>94.5</v>
+        <v>96</v>
       </c>
       <c r="R5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T5">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="U5">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="V5">
-        <v>33.5</v>
+        <v>37</v>
       </c>
       <c r="W5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Z5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="AB5">
-        <v>93</v>
+        <v>91.5</v>
       </c>
       <c r="AC5">
         <v>42.5</v>
       </c>
       <c r="AD5">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="AE5">
-        <v>42.5</v>
+        <v>41.5</v>
       </c>
       <c r="AF5">
-        <v>46.5</v>
+        <v>51</v>
       </c>
       <c r="AG5">
         <v>9.5</v>
       </c>
       <c r="AH5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AI5">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AJ5">
         <v>9</v>
@@ -1311,123 +1284,123 @@
         <v>9.5</v>
       </c>
       <c r="AL5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM5">
         <v>18</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6">
-        <v>0.32545617293022139</v>
+        <v>0.34210564989111703</v>
       </c>
       <c r="D6">
-        <v>72.2</v>
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>182.5</v>
+        <v>188</v>
       </c>
       <c r="F6">
-        <v>132</v>
+        <v>136.5</v>
       </c>
       <c r="G6">
         <v>38</v>
       </c>
       <c r="H6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="K6">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="L6">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>17</v>
       </c>
       <c r="N6">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O6">
-        <v>91</v>
+        <v>86.5</v>
       </c>
       <c r="P6">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="Q6">
         <v>93</v>
       </c>
       <c r="R6">
-        <v>53.5</v>
+        <v>56</v>
       </c>
       <c r="S6">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="T6">
+        <v>40</v>
+      </c>
+      <c r="U6">
+        <v>38</v>
+      </c>
+      <c r="V6">
         <v>37.5</v>
       </c>
-      <c r="U6">
-        <v>36</v>
-      </c>
-      <c r="V6">
-        <v>37</v>
-      </c>
       <c r="W6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="X6">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
       <c r="Y6">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="Z6">
-        <v>29.5</v>
+        <v>32.5</v>
       </c>
       <c r="AA6">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="AB6">
-        <v>92.5</v>
+        <v>96</v>
       </c>
       <c r="AC6">
         <v>43.5</v>
       </c>
       <c r="AD6">
-        <v>49.5</v>
+        <v>53</v>
       </c>
       <c r="AE6">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="AF6">
         <v>47</v>
       </c>
       <c r="AG6">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AH6">
         <v>10.5</v>
@@ -1436,915 +1409,836 @@
         <v>7.5</v>
       </c>
       <c r="AJ6">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AK6">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AL6">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AM6">
         <v>17.5</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="2">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="E7" s="2">
+        <v>178</v>
+      </c>
+      <c r="G7">
+        <v>38</v>
+      </c>
+      <c r="H7">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>26</v>
+      </c>
+      <c r="K7">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>23</v>
+      </c>
+      <c r="M7">
+        <v>17</v>
+      </c>
+      <c r="N7">
+        <v>94</v>
+      </c>
+      <c r="O7">
+        <v>89</v>
+      </c>
+      <c r="P7">
+        <v>76</v>
+      </c>
+      <c r="Q7">
+        <v>94</v>
+      </c>
+      <c r="R7">
+        <v>53.5</v>
+      </c>
+      <c r="S7">
+        <v>48</v>
+      </c>
+      <c r="T7">
+        <v>40</v>
+      </c>
+      <c r="V7">
+        <v>38</v>
+      </c>
+      <c r="W7">
+        <v>30</v>
+      </c>
+      <c r="X7">
+        <v>21.5</v>
+      </c>
+      <c r="Y7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="5">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="E8" s="5">
+        <v>176.5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>130</v>
+      </c>
+      <c r="G8" s="5">
+        <v>40</v>
+      </c>
+      <c r="H8" s="5">
+        <v>31</v>
+      </c>
+      <c r="I8" s="5">
+        <v>32</v>
+      </c>
+      <c r="J8" s="5">
+        <v>28</v>
+      </c>
+      <c r="K8" s="5">
+        <v>28</v>
+      </c>
+      <c r="L8" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="M8" s="5">
+        <v>18</v>
+      </c>
+      <c r="N8" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="O8" s="5">
+        <v>95.5</v>
+      </c>
+      <c r="P8" s="5">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>98</v>
+      </c>
+      <c r="R8" s="5">
+        <v>56</v>
+      </c>
+      <c r="S8" s="5">
+        <v>54.5</v>
+      </c>
+      <c r="T8" s="5">
+        <v>39</v>
+      </c>
+      <c r="U8" s="5">
+        <v>37</v>
+      </c>
+      <c r="V8" s="5">
+        <v>38</v>
+      </c>
+      <c r="W8" s="5">
+        <v>33</v>
+      </c>
+      <c r="X8" s="5">
+        <v>23</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>31</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>27</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>89</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>40.5</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>50.5</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>46</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>49</v>
+      </c>
+      <c r="AG8" s="5">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>0.38289708888324803</v>
-      </c>
-      <c r="D7">
-        <v>91.9</v>
-      </c>
-      <c r="E7">
-        <v>184</v>
-      </c>
-      <c r="F7">
-        <v>133.5</v>
-      </c>
-      <c r="G7">
-        <v>40.5</v>
-      </c>
-      <c r="H7">
-        <v>34</v>
-      </c>
-      <c r="I7">
-        <v>36</v>
-      </c>
-      <c r="J7">
-        <v>32.5</v>
-      </c>
-      <c r="K7">
-        <v>30.5</v>
-      </c>
-      <c r="L7">
-        <v>28.5</v>
-      </c>
-      <c r="M7">
-        <v>19</v>
-      </c>
-      <c r="N7">
-        <v>102</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>84.5</v>
-      </c>
-      <c r="Q7">
-        <v>107.5</v>
-      </c>
-      <c r="R7">
-        <v>64</v>
-      </c>
-      <c r="S7">
-        <v>59</v>
-      </c>
-      <c r="T7">
-        <v>44.5</v>
-      </c>
-      <c r="U7">
-        <v>41</v>
-      </c>
-      <c r="V7">
-        <v>41</v>
-      </c>
-      <c r="W7">
-        <v>38</v>
-      </c>
-      <c r="X7">
-        <v>25</v>
-      </c>
-      <c r="Y7">
-        <v>28</v>
-      </c>
-      <c r="Z7">
-        <v>33.5</v>
-      </c>
-      <c r="AA7">
-        <v>26.5</v>
-      </c>
-      <c r="AB7">
-        <v>94</v>
-      </c>
-      <c r="AC7">
-        <v>42</v>
-      </c>
-      <c r="AD7">
-        <v>51.5</v>
-      </c>
-      <c r="AE7">
-        <v>44</v>
-      </c>
-      <c r="AF7">
-        <v>49.5</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>12</v>
-      </c>
-      <c r="AI7">
+      <c r="AH8" s="5">
+        <v>11</v>
+      </c>
+      <c r="AI8" s="5">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="AK8" s="5">
         <v>9</v>
       </c>
-      <c r="AJ7">
-        <v>10</v>
-      </c>
-      <c r="AK7">
-        <v>10.5</v>
-      </c>
-      <c r="AL7">
-        <v>11</v>
-      </c>
-      <c r="AM7">
-        <v>19</v>
-      </c>
-      <c r="AN7">
-        <v>19.5</v>
-      </c>
-      <c r="AO7">
-        <v>12</v>
-      </c>
-      <c r="AP7">
-        <v>12</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8">
-        <v>0.30559471483346912</v>
-      </c>
-      <c r="D8">
-        <v>60.5</v>
-      </c>
-      <c r="E8">
-        <v>172</v>
-      </c>
-      <c r="F8">
-        <v>123.5</v>
-      </c>
-      <c r="G8">
-        <v>31</v>
-      </c>
-      <c r="H8">
-        <v>26.5</v>
-      </c>
-      <c r="I8">
-        <v>27</v>
-      </c>
-      <c r="J8">
-        <v>24</v>
-      </c>
-      <c r="K8">
-        <v>23.5</v>
-      </c>
-      <c r="L8">
-        <v>21.5</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-      <c r="N8">
-        <v>87</v>
-      </c>
-      <c r="O8">
-        <v>85.5</v>
-      </c>
-      <c r="P8">
-        <v>67</v>
-      </c>
-      <c r="Q8">
-        <v>93</v>
-      </c>
-      <c r="R8">
-        <v>55</v>
-      </c>
-      <c r="S8">
-        <v>53.5</v>
-      </c>
-      <c r="T8">
-        <v>38.5</v>
-      </c>
-      <c r="U8">
-        <v>35.5</v>
-      </c>
-      <c r="V8">
-        <v>35.5</v>
-      </c>
-      <c r="W8">
-        <v>34</v>
-      </c>
-      <c r="X8">
-        <v>22.5</v>
-      </c>
-      <c r="Y8">
-        <v>25</v>
-      </c>
-      <c r="Z8">
-        <v>30.5</v>
-      </c>
-      <c r="AA8">
-        <v>24</v>
-      </c>
-      <c r="AB8">
-        <v>91.5</v>
-      </c>
-      <c r="AC8">
-        <v>42.5</v>
-      </c>
-      <c r="AD8">
-        <v>49.5</v>
-      </c>
-      <c r="AE8">
-        <v>42.5</v>
-      </c>
-      <c r="AF8">
-        <v>44</v>
-      </c>
-      <c r="AG8">
-        <v>8</v>
-      </c>
-      <c r="AH8">
-        <v>8.5</v>
-      </c>
-      <c r="AI8">
-        <v>7</v>
-      </c>
-      <c r="AJ8">
-        <v>7</v>
-      </c>
-      <c r="AK8">
-        <v>8</v>
-      </c>
-      <c r="AL8">
-        <v>8.5</v>
-      </c>
-      <c r="AM8">
-        <v>17</v>
-      </c>
-      <c r="AN8">
-        <v>17.5</v>
-      </c>
-      <c r="AO8">
-        <v>11</v>
-      </c>
-      <c r="AP8">
-        <v>11</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>71</v>
+      <c r="AL8" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="AP8" s="5">
+        <v>11.5</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9">
+        <v>0.34157138849180374</v>
+      </c>
+      <c r="D9">
+        <v>73.3</v>
+      </c>
+      <c r="E9">
+        <v>183</v>
+      </c>
+      <c r="F9">
+        <v>133</v>
+      </c>
+      <c r="G9">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>30.5</v>
+      </c>
+      <c r="I9">
+        <v>31.5</v>
+      </c>
+      <c r="J9">
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <v>27.5</v>
+      </c>
+      <c r="L9">
+        <v>26.5</v>
+      </c>
+      <c r="M9">
+        <v>17.5</v>
+      </c>
+      <c r="N9">
+        <v>94</v>
+      </c>
+      <c r="O9">
+        <v>89</v>
+      </c>
+      <c r="P9">
+        <v>75.5</v>
+      </c>
+      <c r="Q9">
+        <v>94.5</v>
+      </c>
+      <c r="R9">
         <v>57</v>
       </c>
-      <c r="C9">
-        <v>0.31024034415037877</v>
-      </c>
-      <c r="D9">
-        <v>69.7</v>
-      </c>
-      <c r="E9">
-        <v>173.5</v>
-      </c>
-      <c r="F9">
-        <v>128</v>
-      </c>
-      <c r="G9">
-        <v>32</v>
-      </c>
-      <c r="H9">
-        <v>28.5</v>
-      </c>
-      <c r="I9">
-        <v>29</v>
-      </c>
-      <c r="J9">
-        <v>25.5</v>
-      </c>
-      <c r="K9">
-        <v>25.5</v>
-      </c>
-      <c r="L9">
-        <v>23</v>
-      </c>
-      <c r="M9">
-        <v>15.5</v>
-      </c>
-      <c r="N9">
-        <v>89</v>
-      </c>
-      <c r="O9">
-        <v>86</v>
-      </c>
-      <c r="P9">
-        <v>74.5</v>
-      </c>
-      <c r="Q9">
-        <v>103</v>
-      </c>
-      <c r="R9">
-        <v>61</v>
-      </c>
       <c r="S9">
-        <v>55.5</v>
+        <v>57</v>
       </c>
       <c r="T9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V9">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="W9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X9">
         <v>22</v>
       </c>
       <c r="Y9">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="Z9">
-        <v>30.5</v>
+        <v>33</v>
       </c>
       <c r="AA9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB9">
-        <v>90.5</v>
+        <v>93</v>
       </c>
       <c r="AC9">
-        <v>44</v>
+        <v>42.5</v>
       </c>
       <c r="AD9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="AF9">
-        <v>44</v>
+        <v>46.5</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AH9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI9">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ9">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AK9">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AL9">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AM9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO9">
         <v>10.5</v>
       </c>
       <c r="AP9">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10">
-        <v>0.29385459112102713</v>
+        <v>0.32545617293022139</v>
       </c>
       <c r="D10">
-        <v>62.6</v>
+        <v>72.2</v>
       </c>
       <c r="E10">
-        <v>166</v>
+        <v>182.5</v>
       </c>
       <c r="F10">
-        <v>123.5</v>
+        <v>132</v>
       </c>
       <c r="G10">
-        <v>33.5</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="I10">
-        <v>28.5</v>
+        <v>31</v>
       </c>
       <c r="J10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K10">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="L10">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M10">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="N10">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="O10">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="P10">
-        <v>67</v>
+        <v>76.5</v>
       </c>
       <c r="Q10">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R10">
-        <v>57.5</v>
+        <v>53.5</v>
       </c>
       <c r="S10">
-        <v>55</v>
+        <v>53.5</v>
       </c>
       <c r="T10">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="U10">
-        <v>30.5</v>
+        <v>36</v>
       </c>
       <c r="V10">
-        <v>34.5</v>
+        <v>37</v>
       </c>
       <c r="W10">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="X10">
         <v>21.5</v>
       </c>
       <c r="Y10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z10">
         <v>29.5</v>
       </c>
       <c r="AA10">
-        <v>23.5</v>
+        <v>26.5</v>
       </c>
       <c r="AB10">
-        <v>87</v>
+        <v>92.5</v>
       </c>
       <c r="AC10">
-        <v>41.8</v>
+        <v>43.5</v>
       </c>
       <c r="AD10">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="AE10">
-        <v>39.5</v>
+        <v>43.5</v>
       </c>
       <c r="AF10">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AG10">
         <v>8.5</v>
       </c>
       <c r="AH10">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="AI10">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10">
         <v>8</v>
       </c>
       <c r="AK10">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AL10">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AM10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AN10">
         <v>18.5</v>
       </c>
       <c r="AO10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>0.37592844450975937</v>
+        <v>0.38289708888324803</v>
       </c>
       <c r="D11">
-        <v>80.5</v>
+        <v>91.9</v>
       </c>
       <c r="E11">
-        <v>175.5</v>
+        <v>184</v>
       </c>
       <c r="F11">
-        <v>132</v>
+        <v>133.5</v>
       </c>
       <c r="G11">
+        <v>40.5</v>
+      </c>
+      <c r="H11">
         <v>34</v>
       </c>
-      <c r="H11">
-        <v>31</v>
-      </c>
       <c r="I11">
-        <v>31.5</v>
+        <v>36</v>
       </c>
       <c r="J11">
+        <v>32.5</v>
+      </c>
+      <c r="K11">
+        <v>30.5</v>
+      </c>
+      <c r="L11">
+        <v>28.5</v>
+      </c>
+      <c r="M11">
+        <v>19</v>
+      </c>
+      <c r="N11">
+        <v>102</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>84.5</v>
+      </c>
+      <c r="Q11">
+        <v>107.5</v>
+      </c>
+      <c r="R11">
+        <v>64</v>
+      </c>
+      <c r="S11">
+        <v>59</v>
+      </c>
+      <c r="T11">
+        <v>44.5</v>
+      </c>
+      <c r="U11">
+        <v>41</v>
+      </c>
+      <c r="V11">
+        <v>41</v>
+      </c>
+      <c r="W11">
+        <v>38</v>
+      </c>
+      <c r="X11">
+        <v>25</v>
+      </c>
+      <c r="Y11">
         <v>28</v>
       </c>
-      <c r="K11">
-        <v>27</v>
-      </c>
-      <c r="L11">
-        <v>23.5</v>
-      </c>
-      <c r="M11">
-        <v>16.5</v>
-      </c>
-      <c r="N11">
-        <v>93</v>
-      </c>
-      <c r="O11">
-        <v>90</v>
-      </c>
-      <c r="P11">
-        <v>79.5</v>
-      </c>
-      <c r="Q11">
-        <v>111</v>
-      </c>
-      <c r="R11">
-        <v>66.5</v>
-      </c>
-      <c r="S11">
-        <v>60</v>
-      </c>
-      <c r="T11">
-        <v>43.5</v>
-      </c>
-      <c r="U11">
-        <v>38.5</v>
-      </c>
-      <c r="V11">
-        <v>40</v>
-      </c>
-      <c r="W11">
-        <v>37.5</v>
-      </c>
-      <c r="X11">
-        <v>23</v>
-      </c>
-      <c r="Y11">
-        <v>25.5</v>
-      </c>
       <c r="Z11">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="AA11">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="AB11">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AC11">
         <v>42</v>
       </c>
       <c r="AD11">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
       <c r="AE11">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="AF11">
-        <v>46</v>
+        <v>49.5</v>
       </c>
       <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>12</v>
+      </c>
+      <c r="AI11">
         <v>9</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11">
+        <v>10</v>
+      </c>
+      <c r="AK11">
+        <v>10.5</v>
+      </c>
+      <c r="AL11">
         <v>11</v>
-      </c>
-      <c r="AI11">
-        <v>7.5</v>
-      </c>
-      <c r="AJ11">
-        <v>8</v>
-      </c>
-      <c r="AK11">
-        <v>8.5</v>
-      </c>
-      <c r="AL11">
-        <v>9.5</v>
       </c>
       <c r="AM11">
         <v>19</v>
       </c>
       <c r="AN11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP11">
         <v>12</v>
       </c>
       <c r="AQ11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12">
-        <v>0.37670398525069804</v>
-      </c>
-      <c r="D12">
-        <v>70.099999999999994</v>
-      </c>
-      <c r="E12">
-        <v>169.8</v>
-      </c>
-      <c r="F12">
-        <v>126.5</v>
-      </c>
-      <c r="G12">
+        <v>58</v>
+      </c>
+      <c r="D12" s="5">
+        <v>91.2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>182.5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>133</v>
+      </c>
+      <c r="G12" s="5">
+        <v>39</v>
+      </c>
+      <c r="H12" s="5">
         <v>34</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="5">
+        <v>35.5</v>
+      </c>
+      <c r="J12" s="5">
         <v>30</v>
       </c>
-      <c r="I12">
+      <c r="K12" s="5">
         <v>31</v>
       </c>
-      <c r="J12">
-        <v>26.5</v>
-      </c>
-      <c r="K12">
-        <v>25</v>
-      </c>
-      <c r="L12">
-        <v>23</v>
-      </c>
-      <c r="M12">
-        <v>15</v>
-      </c>
-      <c r="N12">
-        <v>91</v>
-      </c>
-      <c r="O12">
-        <v>89.5</v>
-      </c>
-      <c r="P12">
-        <v>72</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>60.5</v>
-      </c>
-      <c r="S12">
-        <v>59</v>
-      </c>
-      <c r="T12">
+      <c r="L12" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>18</v>
+      </c>
+      <c r="N12" s="5">
+        <v>101</v>
+      </c>
+      <c r="O12" s="5">
+        <v>98</v>
+      </c>
+      <c r="P12" s="5">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>108</v>
+      </c>
+      <c r="R12" s="5">
+        <v>65.5</v>
+      </c>
+      <c r="S12" s="5">
+        <v>64</v>
+      </c>
+      <c r="T12" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="U12" s="5">
+        <v>39.5</v>
+      </c>
+      <c r="V12" s="5">
+        <v>38</v>
+      </c>
+      <c r="W12" s="5">
+        <v>32</v>
+      </c>
+      <c r="X12" s="5">
+        <v>24</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>26</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>35</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>101.5</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>50</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>51.5</v>
+      </c>
+      <c r="AE12" s="5">
         <v>42.5</v>
       </c>
-      <c r="U12">
-        <v>39</v>
-      </c>
-      <c r="V12">
-        <v>37</v>
-      </c>
-      <c r="W12">
-        <v>34.5</v>
-      </c>
-      <c r="X12">
-        <v>23</v>
-      </c>
-      <c r="Y12">
-        <v>25.5</v>
-      </c>
-      <c r="Z12">
-        <v>29</v>
-      </c>
-      <c r="AA12">
-        <v>24</v>
-      </c>
-      <c r="AB12">
-        <v>88</v>
-      </c>
-      <c r="AC12">
-        <v>41</v>
-      </c>
-      <c r="AD12">
+      <c r="AF12" s="5">
         <v>47.5</v>
       </c>
-      <c r="AE12">
-        <v>41.5</v>
-      </c>
-      <c r="AF12">
-        <v>45</v>
-      </c>
-      <c r="AG12">
+      <c r="AG12" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" s="5">
+        <v>12.5</v>
+      </c>
+      <c r="AI12" s="5">
+        <v>9</v>
+      </c>
+      <c r="AJ12" s="5">
         <v>9.5</v>
       </c>
-      <c r="AH12">
+      <c r="AK12" s="5">
         <v>10</v>
       </c>
-      <c r="AI12">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12">
-        <v>8</v>
-      </c>
-      <c r="AK12">
-        <v>8.5</v>
-      </c>
-      <c r="AL12">
-        <v>9</v>
-      </c>
-      <c r="AM12">
-        <v>17</v>
-      </c>
-      <c r="AN12">
-        <v>19.5</v>
-      </c>
-      <c r="AO12">
-        <v>11</v>
-      </c>
-      <c r="AP12">
-        <v>11</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>63</v>
+      <c r="AL12" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="AM12" s="5">
+        <v>20</v>
+      </c>
+      <c r="AN12" s="5">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="5">
+        <v>12</v>
+      </c>
+      <c r="AP12" s="5">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>0.31009124794591925</v>
+        <v>0.30559471483346912</v>
       </c>
       <c r="D13">
-        <v>64.2</v>
+        <v>60.5</v>
       </c>
       <c r="E13">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F13">
-        <v>123</v>
+        <v>123.5</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="I13">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K13">
+        <v>23.5</v>
+      </c>
+      <c r="L13">
+        <v>21.5</v>
+      </c>
+      <c r="M13">
+        <v>15</v>
+      </c>
+      <c r="N13">
+        <v>87</v>
+      </c>
+      <c r="O13">
+        <v>85.5</v>
+      </c>
+      <c r="P13">
+        <v>67</v>
+      </c>
+      <c r="Q13">
+        <v>93</v>
+      </c>
+      <c r="R13">
+        <v>55</v>
+      </c>
+      <c r="S13">
+        <v>53.5</v>
+      </c>
+      <c r="T13">
+        <v>38.5</v>
+      </c>
+      <c r="U13">
+        <v>35.5</v>
+      </c>
+      <c r="V13">
+        <v>35.5</v>
+      </c>
+      <c r="W13">
+        <v>34</v>
+      </c>
+      <c r="X13">
+        <v>22.5</v>
+      </c>
+      <c r="Y13">
         <v>25</v>
       </c>
-      <c r="L13">
-        <v>22.5</v>
-      </c>
-      <c r="M13">
-        <v>15.2</v>
-      </c>
-      <c r="N13">
-        <v>86</v>
-      </c>
-      <c r="O13">
-        <v>80</v>
-      </c>
-      <c r="P13">
-        <v>70</v>
-      </c>
-      <c r="Q13">
-        <v>99</v>
-      </c>
-      <c r="R13">
-        <v>61</v>
-      </c>
-      <c r="S13">
-        <v>57</v>
-      </c>
-      <c r="T13">
-        <v>41</v>
-      </c>
-      <c r="U13">
-        <v>38.5</v>
-      </c>
-      <c r="V13">
-        <v>37</v>
-      </c>
-      <c r="W13">
-        <v>33</v>
-      </c>
-      <c r="X13">
-        <v>20</v>
-      </c>
-      <c r="Y13">
-        <v>23</v>
-      </c>
       <c r="Z13">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="AA13">
         <v>24</v>
       </c>
       <c r="AB13">
-        <v>87.5</v>
+        <v>91.5</v>
       </c>
       <c r="AC13">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="AD13">
-        <v>46</v>
+        <v>49.5</v>
       </c>
       <c r="AE13">
-        <v>39</v>
+        <v>42.5</v>
+      </c>
+      <c r="AF13">
+        <v>44</v>
       </c>
       <c r="AG13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH13">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI13">
         <v>7</v>
@@ -2353,123 +2247,123 @@
         <v>7</v>
       </c>
       <c r="AK13">
+        <v>8</v>
+      </c>
+      <c r="AL13">
         <v>8.5</v>
       </c>
-      <c r="AL13">
-        <v>9</v>
-      </c>
       <c r="AM13">
+        <v>17</v>
+      </c>
+      <c r="AN13">
         <v>17.5</v>
       </c>
-      <c r="AN13">
-        <v>19.5</v>
-      </c>
       <c r="AO13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP13">
         <v>11</v>
       </c>
       <c r="AQ13" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14">
-        <v>0.37410241680137873</v>
+        <v>0.31024034415037877</v>
       </c>
       <c r="D14" s="1">
-        <v>84.2</v>
+        <v>69.7</v>
       </c>
       <c r="E14" s="1">
-        <v>180</v>
+        <v>173.5</v>
       </c>
       <c r="F14">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H14">
-        <v>31</v>
+        <v>28.5</v>
       </c>
       <c r="I14">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="J14">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="K14">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="L14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M14">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="N14">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P14">
-        <v>81</v>
+        <v>74.5</v>
       </c>
       <c r="Q14">
         <v>103</v>
       </c>
       <c r="R14">
-        <v>66.5</v>
+        <v>61</v>
       </c>
       <c r="S14">
-        <v>62.5</v>
+        <v>55.5</v>
       </c>
       <c r="T14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="U14">
-        <v>39.5</v>
+        <v>35</v>
       </c>
       <c r="V14">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="W14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="Z14">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="AA14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB14">
-        <v>95</v>
+        <v>90.5</v>
       </c>
       <c r="AC14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AD14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AE14">
+        <v>42</v>
+      </c>
+      <c r="AF14">
         <v>44</v>
-      </c>
-      <c r="AF14">
-        <v>45.5</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2478,35 +2372,988 @@
         <v>10.5</v>
       </c>
       <c r="AI14">
+        <v>7</v>
+      </c>
+      <c r="AJ14">
         <v>7.5</v>
       </c>
-      <c r="AJ14">
+      <c r="AK14">
         <v>8</v>
       </c>
-      <c r="AK14">
+      <c r="AL14">
+        <v>8.5</v>
+      </c>
+      <c r="AM14">
+        <v>16</v>
+      </c>
+      <c r="AN14">
+        <v>18.5</v>
+      </c>
+      <c r="AO14">
+        <v>10.5</v>
+      </c>
+      <c r="AP14">
+        <v>10.6</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15">
+        <v>0.29385459112102713</v>
+      </c>
+      <c r="D15" s="1">
+        <v>62.6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>166</v>
+      </c>
+      <c r="F15" s="1">
+        <v>123.5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>33.5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>27.5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>25</v>
+      </c>
+      <c r="K15" s="1">
+        <v>24</v>
+      </c>
+      <c r="L15" s="1">
+        <v>23</v>
+      </c>
+      <c r="M15" s="6">
+        <v>15.5</v>
+      </c>
+      <c r="N15" s="6">
+        <v>85</v>
+      </c>
+      <c r="O15" s="6">
+        <v>84</v>
+      </c>
+      <c r="P15" s="6">
+        <v>67</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>96</v>
+      </c>
+      <c r="R15" s="6">
+        <v>57.5</v>
+      </c>
+      <c r="S15" s="6">
+        <v>55</v>
+      </c>
+      <c r="T15" s="6">
+        <v>39.5</v>
+      </c>
+      <c r="U15" s="6">
+        <v>30.5</v>
+      </c>
+      <c r="V15" s="6">
+        <v>34.5</v>
+      </c>
+      <c r="W15" s="6">
+        <v>31.5</v>
+      </c>
+      <c r="X15" s="6">
+        <v>21.5</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>24</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>29.5</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>23.5</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>87</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>42</v>
+      </c>
+      <c r="AG15" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL15" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="AM15" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="AN15" s="6">
+        <v>18.5</v>
+      </c>
+      <c r="AO15" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="AP15" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="3">
+        <v>60.2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>164</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3">
+        <v>27</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>25</v>
+      </c>
+      <c r="K16" s="3">
+        <v>25</v>
+      </c>
+      <c r="L16" s="3">
+        <v>22</v>
+      </c>
+      <c r="M16" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4">
+        <v>95</v>
+      </c>
+      <c r="R16" s="4">
+        <v>57</v>
+      </c>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+      <c r="AQ16" s="4"/>
+    </row>
+    <row r="17" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="3">
+        <v>76</v>
+      </c>
+      <c r="E17" s="3">
+        <v>175.5</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3">
+        <v>34.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>26</v>
+      </c>
+      <c r="K17" s="3">
+        <v>37</v>
+      </c>
+      <c r="L17" s="3">
+        <v>21</v>
+      </c>
+      <c r="M17" s="4">
+        <v>17.5</v>
+      </c>
+      <c r="N17" s="4">
+        <v>98</v>
+      </c>
+      <c r="O17" s="4">
+        <v>94</v>
+      </c>
+      <c r="P17" s="4">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>103</v>
+      </c>
+      <c r="R17" s="4">
+        <v>64</v>
+      </c>
+      <c r="S17" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="T17" s="4">
+        <v>44.5</v>
+      </c>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="4">
+        <v>46</v>
+      </c>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+      <c r="AK17" s="4"/>
+      <c r="AL17" s="4"/>
+      <c r="AM17" s="4"/>
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+      <c r="AQ17" s="4"/>
+    </row>
+    <row r="18" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="3">
+        <v>71</v>
+      </c>
+      <c r="E18" s="3">
+        <v>171</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3">
+        <v>35</v>
+      </c>
+      <c r="H18" s="3">
+        <v>29</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3">
+        <v>27</v>
+      </c>
+      <c r="K18" s="3">
+        <v>28</v>
+      </c>
+      <c r="L18" s="3">
+        <v>25</v>
+      </c>
+      <c r="M18" s="4">
+        <v>16.5</v>
+      </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4">
+        <v>101</v>
+      </c>
+      <c r="R18" s="4">
+        <v>58</v>
+      </c>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4">
+        <v>40</v>
+      </c>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
+      <c r="AL18" s="4"/>
+      <c r="AM18" s="4"/>
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="4"/>
+    </row>
+    <row r="19" spans="1:43" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>168</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3">
+        <v>32</v>
+      </c>
+      <c r="H19" s="3">
+        <v>25.5</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3">
+        <v>23.5</v>
+      </c>
+      <c r="K19" s="3">
+        <v>25</v>
+      </c>
+      <c r="L19" s="3">
+        <v>21</v>
+      </c>
+      <c r="M19" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="N19" s="4">
+        <v>87</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4">
+        <v>71</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>98</v>
+      </c>
+      <c r="R19" s="4">
+        <v>55</v>
+      </c>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4">
+        <v>39</v>
+      </c>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="4"/>
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="4"/>
+      <c r="AJ19" s="4"/>
+      <c r="AK19" s="4"/>
+      <c r="AL19" s="4"/>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="4"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20">
+        <v>0.37592844450975937</v>
+      </c>
+      <c r="D20" s="1">
+        <v>80.5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>175.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>132</v>
+      </c>
+      <c r="G20" s="1">
+        <v>34</v>
+      </c>
+      <c r="H20" s="1">
+        <v>31</v>
+      </c>
+      <c r="I20" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>28</v>
+      </c>
+      <c r="K20" s="1">
+        <v>27</v>
+      </c>
+      <c r="L20" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="M20" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="N20" s="6">
+        <v>93</v>
+      </c>
+      <c r="O20" s="6">
+        <v>90</v>
+      </c>
+      <c r="P20" s="6">
+        <v>79.5</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>111</v>
+      </c>
+      <c r="R20" s="6">
+        <v>66.5</v>
+      </c>
+      <c r="S20" s="6">
+        <v>60</v>
+      </c>
+      <c r="T20" s="6">
+        <v>43.5</v>
+      </c>
+      <c r="U20" s="6">
+        <v>38.5</v>
+      </c>
+      <c r="V20" s="6">
+        <v>40</v>
+      </c>
+      <c r="W20" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="X20" s="6">
+        <v>23</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>25.5</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>33</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>24.5</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>88</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>42</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>46</v>
+      </c>
+      <c r="AG20" s="6">
         <v>9</v>
       </c>
-      <c r="AL14">
+      <c r="AH20" s="6">
+        <v>11</v>
+      </c>
+      <c r="AI20" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="AJ20" s="6">
+        <v>8</v>
+      </c>
+      <c r="AK20" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="AL20" s="6">
         <v>9.5</v>
       </c>
-      <c r="AM14">
+      <c r="AM20" s="6">
+        <v>19</v>
+      </c>
+      <c r="AN20" s="6">
+        <v>21</v>
+      </c>
+      <c r="AO20" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="AP20" s="6">
+        <v>12</v>
+      </c>
+      <c r="AQ20" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21">
+        <v>0.37670398525069804</v>
+      </c>
+      <c r="D21" s="1">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="E21" s="1">
+        <v>169.8</v>
+      </c>
+      <c r="F21" s="1">
+        <v>126.5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>34</v>
+      </c>
+      <c r="H21" s="1">
+        <v>30</v>
+      </c>
+      <c r="I21" s="1">
+        <v>31</v>
+      </c>
+      <c r="J21" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>25</v>
+      </c>
+      <c r="L21" s="1">
+        <v>23</v>
+      </c>
+      <c r="M21" s="6">
+        <v>15</v>
+      </c>
+      <c r="N21" s="6">
+        <v>91</v>
+      </c>
+      <c r="O21" s="6">
+        <v>89.5</v>
+      </c>
+      <c r="P21" s="6">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>100</v>
+      </c>
+      <c r="R21" s="6">
+        <v>60.5</v>
+      </c>
+      <c r="S21" s="6">
+        <v>59</v>
+      </c>
+      <c r="T21" s="6">
+        <v>42.5</v>
+      </c>
+      <c r="U21" s="6">
+        <v>39</v>
+      </c>
+      <c r="V21" s="6">
+        <v>37</v>
+      </c>
+      <c r="W21" s="6">
+        <v>34.5</v>
+      </c>
+      <c r="X21" s="6">
+        <v>23</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>25.5</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>29</v>
+      </c>
+      <c r="AA21" s="6">
+        <v>24</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>88</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>41</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="AF21" s="6">
+        <v>45</v>
+      </c>
+      <c r="AG21" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="AH21" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="AJ21" s="6">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="AL21" s="6">
+        <v>9</v>
+      </c>
+      <c r="AM21" s="6">
+        <v>17</v>
+      </c>
+      <c r="AN21" s="6">
         <v>19.5</v>
       </c>
-      <c r="AN14">
+      <c r="AO21" s="6">
+        <v>11</v>
+      </c>
+      <c r="AP21" s="6">
+        <v>11</v>
+      </c>
+      <c r="AQ21" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22">
+        <v>0.31009124794591925</v>
+      </c>
+      <c r="D22" s="1">
+        <v>64.2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>162</v>
+      </c>
+      <c r="F22" s="1">
+        <v>123</v>
+      </c>
+      <c r="G22" s="1">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1">
+        <v>27.5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>29</v>
+      </c>
+      <c r="J22" s="1">
+        <v>26</v>
+      </c>
+      <c r="K22" s="1">
+        <v>25</v>
+      </c>
+      <c r="L22" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="M22" s="6">
+        <v>15.2</v>
+      </c>
+      <c r="N22" s="6">
+        <v>86</v>
+      </c>
+      <c r="O22" s="6">
+        <v>80</v>
+      </c>
+      <c r="P22" s="6">
+        <v>70</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>99</v>
+      </c>
+      <c r="R22" s="6">
+        <v>61</v>
+      </c>
+      <c r="S22" s="6">
+        <v>57</v>
+      </c>
+      <c r="T22" s="6">
+        <v>41</v>
+      </c>
+      <c r="U22" s="6">
+        <v>38.5</v>
+      </c>
+      <c r="V22" s="6">
+        <v>37</v>
+      </c>
+      <c r="W22" s="6">
+        <v>33</v>
+      </c>
+      <c r="X22" s="6">
+        <v>20</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>23</v>
+      </c>
+      <c r="Z22" s="6">
+        <v>30</v>
+      </c>
+      <c r="AA22" s="6">
+        <v>24</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>42</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>46</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>39</v>
+      </c>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6">
+        <v>9</v>
+      </c>
+      <c r="AH22" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="AI22" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ22" s="6">
+        <v>7</v>
+      </c>
+      <c r="AK22" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="AL22" s="6">
+        <v>9</v>
+      </c>
+      <c r="AM22" s="6">
+        <v>17.5</v>
+      </c>
+      <c r="AN22" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="AO22" s="6">
+        <v>10</v>
+      </c>
+      <c r="AP22" s="6">
+        <v>11</v>
+      </c>
+      <c r="AQ22" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23">
+        <v>0.37410241680137873</v>
+      </c>
+      <c r="D23" s="1">
+        <v>84.2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>180</v>
+      </c>
+      <c r="F23" s="1">
+        <v>134</v>
+      </c>
+      <c r="G23" s="1">
+        <v>36</v>
+      </c>
+      <c r="H23" s="1">
+        <v>31</v>
+      </c>
+      <c r="I23" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="J23" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>28</v>
+      </c>
+      <c r="L23" s="1">
+        <v>24</v>
+      </c>
+      <c r="M23" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="N23" s="6">
+        <v>93</v>
+      </c>
+      <c r="O23" s="6">
+        <v>80</v>
+      </c>
+      <c r="P23" s="6">
+        <v>81</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>103</v>
+      </c>
+      <c r="R23" s="6">
+        <v>66.5</v>
+      </c>
+      <c r="S23" s="6">
+        <v>62.5</v>
+      </c>
+      <c r="T23" s="6">
+        <v>47</v>
+      </c>
+      <c r="U23" s="6">
+        <v>39.5</v>
+      </c>
+      <c r="V23" s="6">
+        <v>40.5</v>
+      </c>
+      <c r="W23" s="6">
+        <v>38</v>
+      </c>
+      <c r="X23" s="6">
+        <v>24</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>26.5</v>
+      </c>
+      <c r="Z23" s="6">
+        <v>32</v>
+      </c>
+      <c r="AA23" s="6">
+        <v>25</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>95</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>46</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>50</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>44</v>
+      </c>
+      <c r="AF23" s="6">
+        <v>45.5</v>
+      </c>
+      <c r="AG23" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH23" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="AI23" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>8</v>
+      </c>
+      <c r="AK23" s="6">
+        <v>9</v>
+      </c>
+      <c r="AL23" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="AM23" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="AN23" s="6">
         <v>20.5</v>
       </c>
-      <c r="AO14">
+      <c r="AO23" s="6">
         <v>12.5</v>
       </c>
-      <c r="AP14">
+      <c r="AP23" s="6">
         <v>12.5</v>
       </c>
-      <c r="AQ14" t="s">
+      <c r="AQ23" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ14" xr:uid="{804CFD34-F887-40CD-BE87-6B54EBE5BE66}"/>
+  <autoFilter ref="A1:AQ14" xr:uid="{804CFD34-F887-40CD-BE87-6B54EBE5BE66}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AQ23">
+      <sortCondition ref="B1:B14"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>